--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findAll-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findAll-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="86">
   <si>
     <t>Statement: WorkoutSessionRepository.findAll(options?) – returns filtered paginated sessions.</t>
   </si>
@@ -187,81 +187,36 @@
     <t>MemberId param</t>
   </si>
   <si>
+    <t>memberId = undefined/empty/char</t>
+  </si>
+  <si>
+    <t>Date range</t>
+  </si>
+  <si>
+    <t>startDate = endDate</t>
+  </si>
+  <si>
+    <t>page/pageSize variants</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>BVA-1</t>
+  </si>
+  <si>
     <t>memberId = undefined</t>
   </si>
   <si>
+    <t>Returns all sessions</t>
+  </si>
+  <si>
     <t>memberId = ""</t>
   </si>
   <si>
-    <t>memberId = "a"</t>
-  </si>
-  <si>
-    <t>StartDate param</t>
-  </si>
-  <si>
-    <t>startDate = undefined</t>
-  </si>
-  <si>
-    <t>EndDate param</t>
-  </si>
-  <si>
-    <t>endDate = undefined</t>
-  </si>
-  <si>
-    <t>Date range</t>
-  </si>
-  <si>
-    <t>startDate = endDate</t>
-  </si>
-  <si>
-    <t>Page params</t>
-  </si>
-  <si>
-    <t>page=undef, size=undef</t>
-  </si>
-  <si>
-    <t>page=undef, size=10</t>
-  </si>
-  <si>
-    <t>page=1, size=undef</t>
-  </si>
-  <si>
-    <t>page = 0</t>
-  </si>
-  <si>
-    <t>page = 1</t>
-  </si>
-  <si>
-    <t>page = 2</t>
-  </si>
-  <si>
-    <t>PageSize param</t>
-  </si>
-  <si>
-    <t>pageSize = 1</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>BVA-1 Undefined</t>
-  </si>
-  <si>
-    <t>Returns all sessions</t>
-  </si>
-  <si>
-    <t>BVA-2 Empty</t>
-  </si>
-  <si>
     <t>Returns items=[]</t>
   </si>
   <si>
-    <t>BVA-3 OneChar</t>
-  </si>
-  <si>
-    <t>Returns items</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
@@ -274,124 +229,10 @@
     <t>No options provided</t>
   </si>
   <si>
-    <t>memberId filter</t>
-  </si>
-  <si>
-    <t>startDate filter</t>
-  </si>
-  <si>
-    <t>endDate filter</t>
-  </si>
-  <si>
-    <t>Filtered in range</t>
-  </si>
-  <si>
-    <t>EC-6</t>
-  </si>
-  <si>
-    <t>Member + Range</t>
-  </si>
-  <si>
-    <t>Filtered by both</t>
-  </si>
-  <si>
-    <t>EC-7</t>
-  </si>
-  <si>
-    <t>page=2, total=25</t>
-  </si>
-  <si>
-    <t>Second page, items=1</t>
-  </si>
-  <si>
-    <t>EC-9</t>
-  </si>
-  <si>
-    <t>Non-existent member</t>
-  </si>
-  <si>
-    <t>Items=[], total=0</t>
-  </si>
-  <si>
-    <t>EC-10</t>
-  </si>
-  <si>
-    <t>Oldest vs Newest session</t>
-  </si>
-  <si>
-    <t>Oldest comes first (ASC)</t>
-  </si>
-  <si>
-    <t>EC-11</t>
-  </si>
-  <si>
-    <t>Paginated query</t>
-  </si>
-  <si>
-    <t>Newest comes first (DESC)</t>
-  </si>
-  <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>Same day sessions</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>All, date ASC</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>BVA-9</t>
-  </si>
-  <si>
-    <t>BVA-10</t>
-  </si>
-  <si>
-    <t>First page</t>
-  </si>
-  <si>
-    <t>BVA-11</t>
-  </si>
-  <si>
-    <t>BVA-12</t>
-  </si>
-  <si>
-    <t>page = 2, total=25</t>
-  </si>
-  <si>
-    <t>Second page</t>
-  </si>
-  <si>
-    <t>BVA-13</t>
-  </si>
-  <si>
-    <t>One item</t>
-  </si>
-  <si>
-    <t>Multiple sessions in DB</t>
-  </si>
-  <si>
-    <t>Ordering logic applied</t>
+    <t>Various options</t>
+  </si>
+  <si>
+    <t>Success</t>
   </si>
   <si>
     <t>Testing</t>
@@ -1270,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1305,10 +1146,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1316,120 +1157,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1440,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1455,7 +1186,7 @@
         <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>32</v>
@@ -1472,13 +1203,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>37</v>
@@ -1489,32 +1220,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1542,10 +1256,10 @@
         <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>32</v>
@@ -1562,13 +1276,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>36</v>
@@ -1582,16 +1296,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>37</v>
@@ -1602,16 +1316,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>37</v>
@@ -1622,16 +1336,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>37</v>
@@ -1642,16 +1356,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>37</v>
@@ -1662,16 +1376,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>37</v>
@@ -1682,16 +1396,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>37</v>
@@ -1702,16 +1416,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>37</v>
@@ -1722,16 +1436,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>37</v>
@@ -1742,16 +1456,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>37</v>
@@ -1765,13 +1479,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>37</v>
@@ -1785,13 +1499,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>37</v>
@@ -1805,13 +1519,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>37</v>
@@ -1825,13 +1539,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>37</v>
@@ -1845,13 +1559,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>37</v>
@@ -1865,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>37</v>
@@ -1885,13 +1599,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>37</v>
@@ -1905,13 +1619,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>37</v>
@@ -1925,13 +1639,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>37</v>
@@ -1945,13 +1659,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>37</v>
@@ -1965,13 +1679,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>37</v>
@@ -1985,13 +1699,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>37</v>
@@ -2005,13 +1719,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>37</v>
@@ -2022,16 +1736,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>37</v>
@@ -2062,16 +1776,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2079,39 +1793,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="B3" s="1">
         <v>24</v>
@@ -2126,19 +1840,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findAll-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/workout-session-repository/findAll-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="86">
-  <si>
-    <t>Statement: WorkoutSessionRepository.findAll(options?) – returns filtered paginated sessions.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="138">
+  <si>
+    <t>Statement: WorkoutSessionRepository.findAll(options?) – Returns a paginated list of workout sessions with their exercises. Supports optional filtering by memberId, startDate, and endDate. Supports pagination via page and pageSize. Unpaginated results are ordered by date ascending; paginated results are ordered by date descending.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: WorkoutSessionListOptions?</t>
+    <t>Input: options?: WorkoutSessionListOptions { memberId?, startDate?, endDate?, page?, pageSize? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. The workout session table may be empty or contain sessions across multiple members and dates.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns paginated filtered results. Ascending by date if unpaginated, Descending if paginated.</t>
+    <t>On success: PageResult returned with items matching the applied filters, total reflecting the full count, and items ordered by date ascending (unpaginated) or date descending (paginated).</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,49 +64,49 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>No options → all sessions, items.length: 2, total: 2, ordered by date ascending</t>
+  </si>
+  <si>
     <t>Filters</t>
   </si>
   <si>
-    <t>No options</t>
-  </si>
-  <si>
-    <t>By memberId</t>
-  </si>
-  <si>
-    <t>By startDate</t>
-  </si>
-  <si>
-    <t>By endDate</t>
-  </si>
-  <si>
-    <t>By date range</t>
-  </si>
-  <si>
-    <t>By member + range</t>
+    <t>memberId: MEMBER_ID → sessions for that member, items.length: 1, items[0].memberId: MEMBER_ID</t>
+  </si>
+  <si>
+    <t>startDate: 2024-06-01 → sessions on or after startDate, items[0].date &gt;= startDate</t>
+  </si>
+  <si>
+    <t>endDate: 2024-06-30 → sessions on or before endDate, items[0].date &lt;= endDate</t>
+  </si>
+  <si>
+    <t>startDate: 2024-01-01, endDate: 2024-12-31 → sessions within range, items[0].date &gt;= startDate and items[0].date &lt;= endDate</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, startDate: 2024-06-01, endDate: 2024-06-30 → sessions for that member within range, items[0].memberId: MEMBER_ID</t>
   </si>
   <si>
     <t>Pagination</t>
   </si>
   <si>
-    <t>Custom page/pageSize</t>
-  </si>
-  <si>
-    <t>Database result</t>
-  </si>
-  <si>
-    <t>Matches found</t>
-  </si>
-  <si>
-    <t>No matches found</t>
+    <t>page: 2, pageSize: 10 → second page subset, items.length: 1, total: 25</t>
+  </si>
+  <si>
+    <t>DB results</t>
+  </si>
+  <si>
+    <t>No matching sessions → empty result, items.length: 0, total: 0</t>
   </si>
   <si>
     <t>Ordering</t>
   </si>
   <si>
-    <t>Unpaginated (ASC)</t>
-  </si>
-  <si>
-    <t>Paginated (DESC)</t>
+    <t>Unpaginated, multiple sessions → items[0].id: "older", items[1].id: "newer", items[0].date &lt; items[1].date (ascending)</t>
+  </si>
+  <si>
+    <t>Paginated (page: 1, pageSize: 10), multiple sessions → items[0].id: "newer", items[1].id: "older", items[0].date &gt; items[1].date (descending)</t>
   </si>
   <si>
     <t>No TC</t>
@@ -124,10 +124,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-8, EC-10</t>
-  </si>
-  <si>
-    <t>All sessions, date ASC</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>no options (2 sessions in DB)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, items[0] equal to MOCK_SESSION_WITH_EXERCISES, items[1] equal to session2, total: 2</t>
   </si>
   <si>
     <t>Passed</t>
@@ -136,46 +139,82 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>memberId="m1"</t>
-  </si>
-  <si>
-    <t>Filtered by member</t>
+    <t>options: { memberId: MEMBER_ID } (1 matching session)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].memberId: MEMBER_ID, items[0] equal to MOCK_SESSION_WITH_EXERCISES, total: 1</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>startDate="2024-06-01"</t>
-  </si>
-  <si>
-    <t>Filtered by start</t>
+    <t>options: { startDate: new Date("2024-06-01") } (1 session on or after startDate)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date &gt;= startDate, total: 1</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>endDate="2024-06-30"</t>
-  </si>
-  <si>
-    <t>Filtered by end</t>
+    <t>options: { endDate: new Date("2024-06-30") } (1 session on or before endDate)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date &lt;= endDate, total: 1</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Date range filter</t>
-  </si>
-  <si>
-    <t>Filtered by range</t>
-  </si>
-  <si>
-    <t>EC-7, EC-11</t>
-  </si>
-  <si>
-    <t>page=1, pageSize=10</t>
-  </si>
-  <si>
-    <t>Filtered items, date DESC</t>
+    <t>options: { startDate: new Date("2024-01-01"), endDate: new Date("2024-12-31") } (1 session within range)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date &gt;= startDate, items[0].date &lt;= endDate, total: 1</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>options: { memberId: MEMBER_ID, startDate: new Date("2024-06-01"), endDate: new Date("2024-06-30") }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].memberId: MEMBER_ID, total: 1</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>options: { page: 2, pageSize: 10 } (25 total sessions)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 25</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>options: { memberId: NONEXISTENT_ID } (no matching sessions)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 0</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>no options, sessions: [olderSession (date: 2024-01-01), newerSession (date: 2024-12-01)]</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, items[0].id: "older", items[1].id: "newer", items[0].date &lt; items[1].date</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>options: { page: 1, pageSize: 10 }, sessions: [newerSession (date: 2024-12-01), olderSession (date: 2024-01-01)]</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, items[0].id: "newer", items[1].id: "older", items[0].date &gt; items[1].date</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -184,55 +223,172 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>MemberId param</t>
-  </si>
-  <si>
-    <t>memberId = undefined/empty/char</t>
-  </si>
-  <si>
-    <t>Date range</t>
-  </si>
-  <si>
-    <t>startDate = endDate</t>
-  </si>
-  <si>
-    <t>page/pageSize variants</t>
+    <t>memberId</t>
+  </si>
+  <si>
+    <t>memberId: undefined (all sessions), memberId: "" (no sessions), memberId: "a" (matching sessions)</t>
+  </si>
+  <si>
+    <t>startDate</t>
+  </si>
+  <si>
+    <t>startDate: undefined (all sessions)</t>
+  </si>
+  <si>
+    <t>endDate</t>
+  </si>
+  <si>
+    <t>endDate: undefined (all sessions)</t>
+  </si>
+  <si>
+    <t>Date boundary</t>
+  </si>
+  <si>
+    <t>startDate equals endDate (same-day sessions only)</t>
+  </si>
+  <si>
+    <t>Pagination combo</t>
+  </si>
+  <si>
+    <t>page: undefined + pageSize: undefined, page: undefined + pageSize: 10, page: 1 + pageSize: undefined</t>
+  </si>
+  <si>
+    <t>Page number</t>
+  </si>
+  <si>
+    <t>page: 0 (first page), page: 1 (first page), page: 2 (second page, empty result)</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>pageSize: 1 (one item per page)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (undef)</t>
+  </si>
+  <si>
+    <t>options: { memberId: undefined } (2 sessions in DB)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, total: 2</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>options: { memberId: "" } (no sessions with that memberId)</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>options: { memberId: "a" } (1 session with matching memberId)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].memberId: MEMBER_ID</t>
+  </si>
+  <si>
+    <t>BVA-2 (undef)</t>
+  </si>
+  <si>
+    <t>options: { startDate: undefined } (2 sessions in DB)</t>
+  </si>
+  <si>
+    <t>BVA-3 (undef)</t>
+  </si>
+  <si>
+    <t>options: { endDate: undefined } (2 sessions in DB)</t>
+  </si>
+  <si>
+    <t>BVA-4 (eq)</t>
+  </si>
+  <si>
+    <t>options: { startDate: new Date("2024-06-01"), endDate: new Date("2024-06-01") } (1 matching session on that day)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].date equal to new Date("2024-06-01")</t>
+  </si>
+  <si>
+    <t>BVA-5 (both undef)</t>
+  </si>
+  <si>
+    <t>options: { page: undefined, pageSize: undefined } (3 sessions in DB)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 3, total: 3</t>
+  </si>
+  <si>
+    <t>BVA-5 (page undef)</t>
+  </si>
+  <si>
+    <t>options: { page: undefined, pageSize: 10 } (2 sessions in DB)</t>
+  </si>
+  <si>
+    <t>BVA-5 (size undef)</t>
+  </si>
+  <si>
+    <t>options: { page: 1, pageSize: undefined } (2 sessions in DB)</t>
+  </si>
+  <si>
+    <t>BVA-6 (p=0)</t>
+  </si>
+  <si>
+    <t>options: { page: 0, pageSize: 10 } (5 total sessions)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 5</t>
+  </si>
+  <si>
+    <t>BVA-6 (p=1)</t>
+  </si>
+  <si>
+    <t>options: { page: 1, pageSize: 10 } (25 total sessions)</t>
+  </si>
+  <si>
+    <t>BVA-6 (p=2)</t>
+  </si>
+  <si>
+    <t>options: { page: 2, pageSize: 10 } (25 total sessions, no items on this page)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 25</t>
+  </si>
+  <si>
+    <t>BVA-7 (s=1)</t>
+  </si>
+  <si>
+    <t>options: { page: 1, pageSize: 1 } (5 total sessions)</t>
+  </si>
+  <si>
+    <t>TC from EC</t>
+  </si>
+  <si>
+    <t>TC from BVA</t>
+  </si>
+  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>memberId = undefined</t>
-  </si>
-  <si>
-    <t>Returns all sessions</t>
-  </si>
-  <si>
-    <t>memberId = ""</t>
-  </si>
-  <si>
-    <t>Returns items=[]</t>
-  </si>
-  <si>
-    <t>TC from EC</t>
-  </si>
-  <si>
-    <t>TC from BVA</t>
-  </si>
-  <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>No options provided</t>
-  </si>
-  <si>
-    <t>Various options</t>
-  </si>
-  <si>
-    <t>Success</t>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
   </si>
   <si>
     <t>Testing</t>
@@ -265,7 +421,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-05</t>
+    <t>REPO-21</t>
   </si>
   <si>
     <t>n/a</t>
@@ -790,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -831,10 +987,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -845,10 +1001,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
@@ -859,10 +1015,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>1</v>
@@ -873,10 +1029,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
@@ -887,10 +1043,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1</v>
@@ -901,10 +1057,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1</v>
@@ -915,10 +1071,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1</v>
@@ -929,10 +1085,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1</v>
@@ -946,23 +1102,9 @@
         <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -974,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1009,13 +1151,13 @@
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1023,16 +1165,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,16 +1182,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,16 +1199,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,16 +1216,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1091,16 +1233,84 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1111,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1121,13 +1331,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1135,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1146,10 +1356,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1157,10 +1367,54 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1171,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1186,7 +1440,7 @@
         <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>32</v>
@@ -1203,16 +1457,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1220,16 +1474,203 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1240,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1256,10 +1697,10 @@
         <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>32</v>
@@ -1276,19 +1717,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1296,19 +1737,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1316,19 +1757,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1336,19 +1777,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1356,19 +1797,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,19 +1817,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1396,19 +1837,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1416,19 +1857,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1436,19 +1877,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1456,19 +1897,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1479,16 +1920,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1499,16 +1940,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1519,16 +1960,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1539,16 +1980,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1559,16 +2000,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1579,16 +2020,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1599,16 +2040,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1619,16 +2060,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1639,16 +2080,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1659,16 +2100,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1679,16 +2120,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1699,56 +2140,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1776,16 +2177,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1793,45 +2194,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="B3" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1840,19 +2241,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
